--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -43308,13 +43308,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O247" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R247" t="n">
-        <v>0.0465112781710091</v>
+        <v>0.04844924809480115</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -43817,12 +43817,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -43856,81 +43856,100 @@
         </is>
       </c>
       <c r="N250" t="n">
+        <v>45</v>
+      </c>
+      <c r="O250" t="n">
+        <v>45</v>
+      </c>
+      <c r="R250" t="n">
+        <v>0.4205196192727506</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP250" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AT250" t="n">
         <v>2</v>
       </c>
-      <c r="O250" t="n">
-        <v>2</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0.008691384892873792</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO250" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP250" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr"/>
-      <c r="AT250" t="n">
-        <v>0</v>
-      </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -43957,17 +43976,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -44001,81 +44020,175 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="O251" t="n">
-        <v>67</v>
-      </c>
-      <c r="R251" t="n">
-        <v>0.01919575548955488</v>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>Invasiv pneumokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN251" t="b">
+        <v>1</v>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR251" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44107,12 +44220,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44137,7 +44250,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -44146,13 +44259,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O252" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="R252" t="n">
-        <v>0.02450425222697299</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -44185,42 +44298,42 @@
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -44252,12 +44365,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -44282,7 +44395,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -44291,93 +44404,81 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="O253" t="n">
-        <v>1</v>
-      </c>
-      <c r="P253" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="R253" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA253" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ253" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS253" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr"/>
       <c r="AT253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -44404,17 +44505,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -44448,173 +44549,81 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="O254" t="n">
-        <v>1</v>
-      </c>
-      <c r="P254" t="n">
-        <v>1</v>
-      </c>
-      <c r="U254" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V254" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W254" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X254" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y254" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z254" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA254" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB254" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD254" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE254" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF254" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG254" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH254" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI254" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM254" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN254" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0.02450425222697299</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ254" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44646,12 +44655,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44676,7 +44685,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -44685,81 +44694,93 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="O255" t="n">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="P255" t="n">
+        <v>1</v>
       </c>
       <c r="R255" t="n">
-        <v>0.01661722117006243</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR255" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44786,17 +44807,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -44821,7 +44842,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -44830,81 +44851,173 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O256" t="n">
-        <v>18</v>
-      </c>
-      <c r="R256" t="n">
-        <v>0.01470255133618379</v>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P256" t="n">
+        <v>1</v>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM256" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN256" t="b">
+        <v>1</v>
       </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -44936,12 +45049,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -44966,7 +45079,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -44975,93 +45088,81 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="O257" t="n">
-        <v>2</v>
-      </c>
-      <c r="P257" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="R257" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.01661722117006243</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA257" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ257" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr"/>
       <c r="AT257" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45088,17 +45189,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45132,173 +45233,81 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O258" t="n">
-        <v>2</v>
-      </c>
-      <c r="P258" t="n">
-        <v>2</v>
-      </c>
-      <c r="U258" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X258" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC258" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD258" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE258" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF258" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG258" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH258" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI258" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM258" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN258" t="b">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0.01470255133618379</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ258" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45330,12 +45339,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45360,7 +45369,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -45369,81 +45378,93 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="O259" t="n">
-        <v>76</v>
+        <v>2</v>
+      </c>
+      <c r="P259" t="n">
+        <v>2</v>
       </c>
       <c r="R259" t="n">
-        <v>0.02177428980904733</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR259" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT259" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45470,17 +45491,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45505,7 +45526,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -45514,81 +45535,173 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="O260" t="n">
-        <v>29</v>
-      </c>
-      <c r="R260" t="n">
-        <v>0.02368744381940722</v>
-      </c>
-      <c r="S260" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P260" t="n">
+        <v>2</v>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ260" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK260" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM260" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN260" t="b">
+        <v>1</v>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR260" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45620,12 +45733,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -45650,7 +45763,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -45659,93 +45772,81 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="O261" t="n">
-        <v>2</v>
-      </c>
-      <c r="P261" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="R261" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.02177428980904733</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA261" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ261" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr"/>
       <c r="AT261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45772,17 +45873,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -45816,173 +45917,81 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="O262" t="n">
-        <v>2</v>
-      </c>
-      <c r="P262" t="n">
-        <v>2</v>
-      </c>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V262" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W262" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X262" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y262" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA262" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB262" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD262" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE262" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF262" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG262" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH262" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI262" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ262" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK262" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM262" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN262" t="b">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="R262" t="n">
+        <v>0.02368744381940722</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ262" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr"/>
       <c r="AT262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46014,12 +46023,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46044,7 +46053,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -46053,81 +46062,93 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="O263" t="n">
-        <v>52</v>
+        <v>2</v>
+      </c>
+      <c r="P263" t="n">
+        <v>2</v>
       </c>
       <c r="R263" t="n">
-        <v>0.0148981982904008</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR263" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT263" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46154,17 +46175,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46189,7 +46210,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -46198,81 +46219,173 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="O264" t="n">
-        <v>19</v>
-      </c>
-      <c r="R264" t="n">
-        <v>0.01551935974374956</v>
-      </c>
-      <c r="S264" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P264" t="n">
+        <v>2</v>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ264" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM264" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN264" t="b">
+        <v>1</v>
       </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR264" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46304,12 +46417,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46334,7 +46447,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -46343,93 +46456,81 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="O265" t="n">
-        <v>2</v>
-      </c>
-      <c r="P265" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="R265" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.0148981982904008</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA265" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ265" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46456,17 +46557,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46500,173 +46601,81 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="O266" t="n">
-        <v>2</v>
-      </c>
-      <c r="P266" t="n">
-        <v>2</v>
-      </c>
-      <c r="U266" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V266" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W266" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X266" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y266" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA266" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD266" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE266" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF266" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG266" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH266" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI266" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ266" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK266" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM266" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN266" t="b">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="R266" t="n">
+        <v>0.01551935974374956</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ266" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr"/>
       <c r="AT266" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46698,12 +46707,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -46728,7 +46737,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -46737,81 +46746,93 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="O267" t="n">
-        <v>67</v>
+        <v>2</v>
+      </c>
+      <c r="P267" t="n">
+        <v>2</v>
       </c>
       <c r="R267" t="n">
-        <v>0.01919575548955488</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR267" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ267" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46838,17 +46859,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -46873,90 +46894,182 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N268" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O268" t="n">
-        <v>4</v>
-      </c>
-      <c r="R268" t="n">
-        <v>0.01469124727807916</v>
-      </c>
-      <c r="S268" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P268" t="n">
+        <v>2</v>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD268" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI268" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ268" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK268" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM268" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN268" t="b">
+        <v>1</v>
       </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR268" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ268" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT268" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46988,12 +47101,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47018,109 +47131,90 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N269" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="O269" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="R269" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="AA269" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ269" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR269" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr"/>
       <c r="AT269" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47147,17 +47241,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47191,175 +47285,81 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O270" t="n">
-        <v>2</v>
-      </c>
-      <c r="U270" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X270" t="inlineStr">
-        <is>
-          <t>Streptococcus pneumoniae</t>
-        </is>
-      </c>
-      <c r="Y270" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA270" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD270" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0.01469124727807916</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr"/>
+      <c r="AT270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU270" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV270" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE270" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF270" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG270" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH270" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI270" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ270" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK270" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
-        </is>
-      </c>
-      <c r="AM270" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN270" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO270" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP270" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ270" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="AT270" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU270" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV270" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47391,12 +47391,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47430,81 +47430,100 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O271" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R271" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR271" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
       <c r="AT271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47531,17 +47550,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -47575,22 +47594,39 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O272" t="n">
-        <v>0</v>
-      </c>
-      <c r="R272" t="n">
-        <v>0</v>
-      </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>Streptococcus pneumoniae</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -47598,6 +47634,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ272" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
+        </is>
+      </c>
+      <c r="AM272" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN272" t="b">
+        <v>1</v>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47610,7 +47704,7 @@
       </c>
       <c r="AQ272" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR272" t="inlineStr">
@@ -47620,7 +47714,7 @@
       </c>
       <c r="AS272" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT272" t="n">
@@ -47628,47 +47722,47 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47695,217 +47789,526 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N273" t="n">
+        <v>2</v>
+      </c>
+      <c r="O273" t="n">
+        <v>2</v>
+      </c>
+      <c r="R273" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr"/>
+      <c r="AT273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV273" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA273" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB273" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC273" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" t="n">
+        <v>0</v>
+      </c>
+      <c r="R274" t="n">
+        <v>0</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV274" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA274" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB274" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC274" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
+      <c r="F275" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
+      <c r="G275" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>D106</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>Invasive pneumococcal disease</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr">
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
         <is>
           <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
+      <c r="K275" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
+      <c r="L275" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M273" t="inlineStr">
+      <c r="M275" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N273" t="n">
+      <c r="N275" t="n">
         <v>0</v>
       </c>
-      <c r="O273" t="n">
+      <c r="O275" t="n">
         <v>0</v>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="U275" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
-      <c r="V273" t="inlineStr">
+      <c r="V275" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
-      <c r="W273" t="inlineStr">
+      <c r="W275" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X273" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>Syst. pneumokokksykdom</t>
         </is>
       </c>
-      <c r="Y273" t="inlineStr">
+      <c r="Y275" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z273" t="inlineStr">
+      <c r="Z275" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA273" t="inlineStr">
+      <c r="AA275" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB273" t="inlineStr">
+      <c r="AB275" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC273" t="inlineStr">
+      <c r="AC275" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD273" t="inlineStr">
+      <c r="AD275" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE273" t="inlineStr">
+      <c r="AE275" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF273" t="inlineStr">
+      <c r="AF275" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG273" t="inlineStr">
+      <c r="AG275" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH273" t="inlineStr">
+      <c r="AH275" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI273" t="inlineStr">
+      <c r="AI275" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ273" t="inlineStr">
+      <c r="AJ275" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK273" t="inlineStr">
+      <c r="AK275" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
         </is>
       </c>
-      <c r="AM273" t="inlineStr">
+      <c r="AM275" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN273" t="b">
+      <c r="AN275" t="b">
         <v>1</v>
       </c>
-      <c r="AO273" t="inlineStr">
+      <c r="AO275" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP273" t="inlineStr">
+      <c r="AP275" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ273" t="inlineStr">
+      <c r="AQ275" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR273" t="inlineStr">
+      <c r="AR275" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS273" t="inlineStr">
+      <c r="AS275" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
-      <c r="AT273" t="n">
+      <c r="AT275" t="n">
         <v>2</v>
       </c>
-      <c r="AU273" t="inlineStr">
+      <c r="AU275" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV273" t="inlineStr">
+      <c r="AV275" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW273" t="inlineStr">
+      <c r="AW275" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX273" t="inlineStr">
+      <c r="AX275" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY273" t="inlineStr">
+      <c r="AY275" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ273" t="inlineStr">
+      <c r="AZ275" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA273" t="inlineStr">
+      <c r="BA275" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB273" t="inlineStr">
+      <c r="BB275" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC273" t="inlineStr">
+      <c r="BC275" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -48027,7 +48430,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -48037,7 +48440,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -48057,7 +48460,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -48089,7 +48492,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12769</v>
+        <v>12817</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -41908,13 +41908,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="O238" t="n">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="R238" t="n">
-        <v>1.021041685826502</v>
+        <v>1.079806674938818</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -47246,12 +47246,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47276,22 +47276,22 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N270" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="O270" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="R270" t="n">
-        <v>0.01469124727807916</v>
+        <v>0.02532106063453875</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -47324,42 +47324,42 @@
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47391,12 +47391,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47430,100 +47430,81 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O271" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R271" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.01469124727807916</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ271" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR271" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr"/>
       <c r="AT271" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47550,7 +47531,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -47594,103 +47575,28 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O272" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0.1067285502518482</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U272" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>Streptococcus pneumoniae</t>
-        </is>
-      </c>
-      <c r="Y272" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG272" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ272" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK272" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
-        </is>
-      </c>
-      <c r="AM272" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN272" t="b">
-        <v>1</v>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
@@ -47789,17 +47695,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -47833,81 +47739,175 @@
         </is>
       </c>
       <c r="N273" t="n">
+        <v>6</v>
+      </c>
+      <c r="O273" t="n">
+        <v>6</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>Streptococcus pneumoniae</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="AT273" t="n">
         <v>2</v>
       </c>
-      <c r="O273" t="n">
-        <v>2</v>
-      </c>
-      <c r="R273" t="n">
-        <v>0.003875939847584092</v>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO273" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP273" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR273" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr"/>
-      <c r="AT273" t="n">
-        <v>0</v>
-      </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47939,12 +47939,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -47978,100 +47978,81 @@
         </is>
       </c>
       <c r="N274" t="n">
+        <v>2</v>
+      </c>
+      <c r="O274" t="n">
+        <v>2</v>
+      </c>
+      <c r="R274" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr"/>
+      <c r="AT274" t="n">
         <v>0</v>
       </c>
-      <c r="O274" t="n">
-        <v>0</v>
-      </c>
-      <c r="R274" t="n">
-        <v>0</v>
-      </c>
-      <c r="S274" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U274" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA274" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO274" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP274" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ274" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR274" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS274" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT274" t="n">
-        <v>2</v>
-      </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -48098,7 +48079,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -48147,98 +48128,23 @@
       <c r="O275" t="n">
         <v>0</v>
       </c>
+      <c r="R275" t="n">
+        <v>0</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U275" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
-      <c r="V275" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W275" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X275" t="inlineStr">
-        <is>
-          <t>Syst. pneumokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y275" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z275" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA275" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB275" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD275" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE275" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF275" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG275" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH275" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI275" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ275" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK275" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
-        </is>
-      </c>
-      <c r="AM275" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN275" t="b">
-        <v>1</v>
       </c>
       <c r="AO275" t="inlineStr">
         <is>
@@ -48309,6 +48215,245 @@
         </is>
       </c>
       <c r="BC275" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N276" t="n">
+        <v>0</v>
+      </c>
+      <c r="O276" t="n">
+        <v>0</v>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>Syst. pneumokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ276" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
+        </is>
+      </c>
+      <c r="AM276" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN276" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP276" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ276" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR276" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU276" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV276" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA276" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB276" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC276" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -48430,7 +48575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -48440,7 +48585,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -48492,7 +48637,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12817</v>
+        <v>12867</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -35706,13 +35706,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O201" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="R201" t="n">
-        <v>1.04675136856314</v>
+        <v>1.05042418038266</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -36990,13 +36990,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O210" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R210" t="n">
-        <v>0.4980665678419585</v>
+        <v>0.5158546595505998</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -37154,10 +37154,10 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O211" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U211" t="inlineStr">
         <is>
@@ -37683,13 +37683,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O214" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R214" t="n">
-        <v>0.7075903303182025</v>
+        <v>0.7252800885761576</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -37847,10 +37847,10 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O215" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U215" t="inlineStr">
         <is>
@@ -41908,13 +41908,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="O238" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="R238" t="n">
-        <v>1.079806674938818</v>
+        <v>1.090825110397378</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -42905,13 +42905,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O245" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R245" t="n">
-        <v>0.4447022927160344</v>
+        <v>0.4980665678419585</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -43069,10 +43069,10 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O246" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="U246" t="inlineStr">
         <is>
@@ -43453,13 +43453,13 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O248" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R248" t="n">
-        <v>0.583762022512517</v>
+        <v>0.6014517807704721</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -43617,10 +43617,10 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O249" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U249" t="inlineStr">
         <is>
@@ -47575,13 +47575,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O272" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R272" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -47739,10 +47739,10 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O273" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U273" t="inlineStr">
         <is>
@@ -47978,13 +47978,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O274" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R274" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -48123,13 +48123,13 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O275" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R275" t="n">
-        <v>0</v>
+        <v>0.1945873408375057</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
@@ -48287,10 +48287,10 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O276" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U276" t="inlineStr">
         <is>
@@ -48637,7 +48637,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12867</v>
+        <v>12891</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -41908,13 +41908,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O238" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="R238" t="n">
-        <v>1.090825110397378</v>
+        <v>1.087152298577858</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -47391,12 +47391,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47421,90 +47421,102 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N271" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O271" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="P271" t="n">
+        <v>2</v>
       </c>
       <c r="R271" t="n">
-        <v>0.01469124727807916</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR271" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47531,17 +47543,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -47566,37 +47578,115 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N272" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O272" t="n">
-        <v>7</v>
-      </c>
-      <c r="R272" t="n">
-        <v>0.1245166419604896</v>
-      </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P272" t="n">
+        <v>2</v>
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1390</t>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ272" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM272" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN272" t="b">
+        <v>1</v>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
@@ -47605,22 +47695,17 @@
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ272" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR272" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS272" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1390</t>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
         </is>
       </c>
       <c r="AT272" t="n">
@@ -47628,47 +47713,47 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47695,17 +47780,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -47739,175 +47824,81 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O273" t="n">
-        <v>7</v>
-      </c>
-      <c r="U273" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="V273" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="W273" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X273" t="inlineStr">
-        <is>
-          <t>Streptococcus pneumoniae</t>
-        </is>
-      </c>
-      <c r="Y273" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z273" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA273" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB273" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD273" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="R273" t="n">
+        <v>0.01469124727807916</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr"/>
+      <c r="AT273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV273" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE273" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF273" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG273" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH273" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI273" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ273" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK273" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
-        </is>
-      </c>
-      <c r="AM273" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN273" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO273" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP273" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ273" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR273" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="AT273" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU273" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV273" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47939,12 +47930,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -47978,81 +47969,100 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O274" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R274" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR274" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS274" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
       <c r="AT274" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48079,17 +48089,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -48123,22 +48133,39 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O275" t="n">
-        <v>11</v>
-      </c>
-      <c r="R275" t="n">
-        <v>0.1945873408375057</v>
-      </c>
-      <c r="S275" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>Streptococcus pneumoniae</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -48146,6 +48173,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ275" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK275" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
+        </is>
+      </c>
+      <c r="AM275" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN275" t="b">
+        <v>1</v>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -48158,7 +48243,7 @@
       </c>
       <c r="AQ275" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR275" t="inlineStr">
@@ -48168,7 +48253,7 @@
       </c>
       <c r="AS275" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT275" t="n">
@@ -48176,47 +48261,47 @@
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48243,219 +48328,673 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N276" t="n">
+        <v>4</v>
+      </c>
+      <c r="O276" t="n">
+        <v>4</v>
+      </c>
+      <c r="R276" t="n">
+        <v>0.007751879695168184</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP276" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR276" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr"/>
+      <c r="AT276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU276" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV276" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA276" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB276" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC276" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N277" t="n">
+        <v>11</v>
+      </c>
+      <c r="O277" t="n">
+        <v>11</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0.1945873408375057</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP277" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR277" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT277" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU277" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV277" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA277" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB277" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC277" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr">
+      <c r="F278" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
+      <c r="G278" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>D106</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>Invasive pneumococcal disease</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr">
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
         <is>
           <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr">
+      <c r="K278" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr">
+      <c r="L278" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M276" t="inlineStr">
+      <c r="M278" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N276" t="n">
+      <c r="N278" t="n">
         <v>11</v>
       </c>
-      <c r="O276" t="n">
+      <c r="O278" t="n">
         <v>11</v>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="U278" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
-      <c r="V276" t="inlineStr">
+      <c r="V278" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
-      <c r="W276" t="inlineStr">
+      <c r="W278" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X276" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>Syst. pneumokokksykdom</t>
         </is>
       </c>
-      <c r="Y276" t="inlineStr">
+      <c r="Y278" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z276" t="inlineStr">
+      <c r="Z278" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA276" t="inlineStr">
+      <c r="AA278" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB276" t="inlineStr">
+      <c r="AB278" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC276" t="inlineStr">
+      <c r="AC278" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD276" t="inlineStr">
+      <c r="AD278" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE276" t="inlineStr">
+      <c r="AE278" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF276" t="inlineStr">
+      <c r="AF278" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG276" t="inlineStr">
+      <c r="AG278" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH276" t="inlineStr">
+      <c r="AH278" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI276" t="inlineStr">
+      <c r="AI278" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ276" t="inlineStr">
+      <c r="AJ278" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK276" t="inlineStr">
+      <c r="AK278" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
         </is>
       </c>
-      <c r="AM276" t="inlineStr">
+      <c r="AM278" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN276" t="b">
+      <c r="AN278" t="b">
         <v>1</v>
       </c>
-      <c r="AO276" t="inlineStr">
+      <c r="AO278" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP276" t="inlineStr">
+      <c r="AP278" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ276" t="inlineStr">
+      <c r="AQ278" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR276" t="inlineStr">
+      <c r="AR278" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS276" t="inlineStr">
+      <c r="AS278" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
-      <c r="AT276" t="n">
+      <c r="AT278" t="n">
         <v>2</v>
       </c>
-      <c r="AU276" t="inlineStr">
+      <c r="AU278" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV276" t="inlineStr">
+      <c r="AV278" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW276" t="inlineStr">
+      <c r="AW278" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX276" t="inlineStr">
+      <c r="AX278" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY276" t="inlineStr">
+      <c r="AY278" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ276" t="inlineStr">
+      <c r="AZ278" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA276" t="inlineStr">
+      <c r="BA278" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB276" t="inlineStr">
+      <c r="BB278" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC276" t="inlineStr">
+      <c r="BC278" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N279" t="n">
+        <v>79</v>
+      </c>
+      <c r="O279" t="n">
+        <v>79</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0.02263380124887814</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr"/>
+      <c r="AT279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV279" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA279" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB279" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC279" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -48492,7 +49031,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -48575,7 +49114,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -48585,7 +49124,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11">
@@ -48605,7 +49144,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -48637,7 +49176,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12891</v>
+        <v>12972</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -48359,13 +48359,13 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O276" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R276" t="n">
-        <v>0.142304733669131</v>
+        <v>0.1600928253777724</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -48523,10 +48523,10 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O277" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U277" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13046</v>
+        <v>13047</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -42298,13 +42298,13 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O240" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="R240" t="n">
-        <v>1.087152298577858</v>
+        <v>1.094497922216898</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13047</v>
+        <v>13049</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -48359,13 +48359,13 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="O276" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="R276" t="n">
-        <v>0.1600928253777724</v>
+        <v>0.3023975590469034</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -48523,10 +48523,10 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="O277" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="U277" t="inlineStr">
         <is>
@@ -48762,13 +48762,13 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O278" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R278" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -49385,6 +49385,151 @@
       <c r="BC281" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>18</v>
+      </c>
+      <c r="O282" t="n">
+        <v>18</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0.01470255133618379</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr"/>
+      <c r="AT282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49421,7 +49566,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -49504,7 +49649,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
@@ -49514,7 +49659,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11">
@@ -49566,7 +49711,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13049</v>
+        <v>13077</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -44207,12 +44207,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44246,13 +44246,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="O252" t="n">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="R252" t="n">
-        <v>0.4205196192727506</v>
+        <v>2.118211722448449</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -44276,7 +44276,7 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
@@ -44284,62 +44284,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS252" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT252" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44371,12 +44366,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -44410,29 +44405,29 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="O253" t="n">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X253" t="inlineStr">
         <is>
-          <t>Invasiv pneumokockinfektion</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="Y253" t="inlineStr">
@@ -44442,7 +44437,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -44457,7 +44452,7 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr">
@@ -44492,17 +44487,17 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+          <t>New Zealand PHF Science monthly invasive pneumococcal disease notifications.</t>
         </is>
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -44515,7 +44510,7 @@
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ253" t="inlineStr">
@@ -44523,62 +44518,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS253" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44610,12 +44600,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -44649,81 +44639,100 @@
         </is>
       </c>
       <c r="N254" t="n">
+        <v>45</v>
+      </c>
+      <c r="O254" t="n">
+        <v>45</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0.4205196192727506</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AT254" t="n">
         <v>2</v>
       </c>
-      <c r="O254" t="n">
-        <v>2</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0.008691384892873792</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP254" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR254" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr"/>
-      <c r="AT254" t="n">
-        <v>0</v>
-      </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44750,17 +44759,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -44794,81 +44803,175 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="O255" t="n">
-        <v>67</v>
-      </c>
-      <c r="R255" t="n">
-        <v>0.01919575548955488</v>
-      </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>Invasiv pneumokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM255" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN255" t="b">
+        <v>1</v>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR255" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44900,12 +45003,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -44930,7 +45033,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -44939,13 +45042,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O256" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="R256" t="n">
-        <v>0.02450425222697299</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -44978,42 +45081,42 @@
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -45045,12 +45148,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -45075,7 +45178,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -45084,93 +45187,81 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="O257" t="n">
-        <v>1</v>
-      </c>
-      <c r="P257" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="R257" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA257" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ257" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr"/>
       <c r="AT257" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45197,17 +45288,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45241,173 +45332,81 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="O258" t="n">
-        <v>1</v>
-      </c>
-      <c r="P258" t="n">
-        <v>1</v>
-      </c>
-      <c r="U258" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X258" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC258" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD258" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE258" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF258" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG258" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH258" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI258" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM258" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN258" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0.02450425222697299</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ258" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS258" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45439,12 +45438,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45469,7 +45468,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -45478,81 +45477,93 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="O259" t="n">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="P259" t="n">
+        <v>1</v>
       </c>
       <c r="R259" t="n">
-        <v>0.01661722117006243</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR259" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT259" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45579,17 +45590,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -45614,7 +45625,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -45623,81 +45634,173 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O260" t="n">
-        <v>18</v>
-      </c>
-      <c r="R260" t="n">
-        <v>0.01470255133618379</v>
-      </c>
-      <c r="S260" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P260" t="n">
+        <v>1</v>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ260" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK260" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM260" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN260" t="b">
+        <v>1</v>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR260" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45729,12 +45832,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -45759,7 +45862,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -45768,93 +45871,81 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="O261" t="n">
-        <v>2</v>
-      </c>
-      <c r="P261" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="R261" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.01661722117006243</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA261" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ261" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr"/>
       <c r="AT261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45881,17 +45972,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -45925,173 +46016,81 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O262" t="n">
-        <v>2</v>
-      </c>
-      <c r="P262" t="n">
-        <v>2</v>
-      </c>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V262" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W262" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X262" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y262" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA262" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB262" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD262" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE262" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF262" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG262" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH262" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI262" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ262" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK262" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM262" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN262" t="b">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="R262" t="n">
+        <v>0.01470255133618379</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ262" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr"/>
       <c r="AT262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46123,12 +46122,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46153,7 +46152,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -46162,81 +46161,93 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="O263" t="n">
-        <v>76</v>
+        <v>2</v>
+      </c>
+      <c r="P263" t="n">
+        <v>2</v>
       </c>
       <c r="R263" t="n">
-        <v>0.02177428980904733</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR263" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT263" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46263,17 +46274,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46298,7 +46309,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -46307,81 +46318,173 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="O264" t="n">
-        <v>29</v>
-      </c>
-      <c r="R264" t="n">
-        <v>0.02368744381940722</v>
-      </c>
-      <c r="S264" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P264" t="n">
+        <v>2</v>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ264" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM264" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN264" t="b">
+        <v>1</v>
       </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR264" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46413,12 +46516,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46443,7 +46546,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -46452,93 +46555,81 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="O265" t="n">
-        <v>2</v>
-      </c>
-      <c r="P265" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="R265" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.02177428980904733</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA265" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ265" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46565,17 +46656,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46609,173 +46700,81 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="O266" t="n">
-        <v>2</v>
-      </c>
-      <c r="P266" t="n">
-        <v>2</v>
-      </c>
-      <c r="U266" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V266" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W266" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X266" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y266" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA266" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD266" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE266" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF266" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG266" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH266" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI266" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ266" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK266" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM266" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN266" t="b">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="R266" t="n">
+        <v>0.02368744381940722</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ266" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr"/>
       <c r="AT266" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46807,12 +46806,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -46837,7 +46836,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -46846,81 +46845,93 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="O267" t="n">
-        <v>52</v>
+        <v>2</v>
+      </c>
+      <c r="P267" t="n">
+        <v>2</v>
       </c>
       <c r="R267" t="n">
-        <v>0.0148981982904008</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR267" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ267" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46947,17 +46958,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -46982,7 +46993,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -46991,81 +47002,173 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="O268" t="n">
-        <v>19</v>
-      </c>
-      <c r="R268" t="n">
-        <v>0.01551935974374956</v>
-      </c>
-      <c r="S268" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P268" t="n">
+        <v>2</v>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD268" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI268" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ268" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK268" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM268" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN268" t="b">
+        <v>1</v>
       </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR268" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ268" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT268" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47097,12 +47200,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47127,7 +47230,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -47136,93 +47239,81 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="O269" t="n">
-        <v>2</v>
-      </c>
-      <c r="P269" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="R269" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.0148981982904008</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA269" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ269" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr"/>
       <c r="AT269" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47249,17 +47340,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47293,173 +47384,81 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="O270" t="n">
-        <v>2</v>
-      </c>
-      <c r="P270" t="n">
-        <v>2</v>
-      </c>
-      <c r="U270" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X270" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y270" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA270" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD270" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE270" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF270" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG270" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH270" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI270" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ270" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK270" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM270" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN270" t="b">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0.01551935974374956</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ270" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr"/>
       <c r="AT270" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47491,12 +47490,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47521,7 +47520,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -47530,81 +47529,93 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="O271" t="n">
-        <v>67</v>
+        <v>2</v>
+      </c>
+      <c r="P271" t="n">
+        <v>2</v>
       </c>
       <c r="R271" t="n">
-        <v>0.01919575548955488</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR271" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47631,17 +47642,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -47666,7 +47677,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -47675,81 +47686,173 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="O272" t="n">
-        <v>31</v>
-      </c>
-      <c r="R272" t="n">
-        <v>0.02532106063453875</v>
-      </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P272" t="n">
+        <v>2</v>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ272" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM272" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN272" t="b">
+        <v>1</v>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR272" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47781,12 +47884,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -47811,7 +47914,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -47820,93 +47923,81 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="O273" t="n">
-        <v>2</v>
-      </c>
-      <c r="P273" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="R273" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA273" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO273" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ273" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr"/>
       <c r="AT273" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47933,17 +48024,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -47977,173 +48068,81 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="O274" t="n">
-        <v>2</v>
-      </c>
-      <c r="P274" t="n">
-        <v>2</v>
-      </c>
-      <c r="U274" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V274" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W274" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X274" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y274" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA274" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB274" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD274" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE274" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF274" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG274" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ274" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK274" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM274" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN274" t="b">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="R274" t="n">
+        <v>0.02532106063453875</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO274" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ274" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS274" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr"/>
       <c r="AT274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48175,12 +48174,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -48205,90 +48204,102 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N275" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O275" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="P275" t="n">
+        <v>2</v>
       </c>
       <c r="R275" t="n">
-        <v>0.01469124727807916</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR275" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS275" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48315,17 +48326,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -48350,37 +48361,115 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N276" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="O276" t="n">
-        <v>17</v>
-      </c>
-      <c r="R276" t="n">
-        <v>0.3023975590469034</v>
-      </c>
-      <c r="S276" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P276" t="n">
+        <v>2</v>
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1390</t>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ276" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM276" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN276" t="b">
+        <v>1</v>
       </c>
       <c r="AO276" t="inlineStr">
         <is>
@@ -48389,22 +48478,17 @@
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ276" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR276" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS276" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1390</t>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
         </is>
       </c>
       <c r="AT276" t="n">
@@ -48412,47 +48496,47 @@
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48479,17 +48563,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -48523,175 +48607,81 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="O277" t="n">
-        <v>17</v>
-      </c>
-      <c r="U277" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="V277" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="W277" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X277" t="inlineStr">
-        <is>
-          <t>Streptococcus pneumoniae</t>
-        </is>
-      </c>
-      <c r="Y277" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA277" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB277" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD277" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0.01469124727807916</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP277" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR277" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr"/>
+      <c r="AT277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU277" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV277" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE277" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF277" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG277" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH277" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI277" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ277" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK277" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
-        </is>
-      </c>
-      <c r="AM277" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN277" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO277" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP277" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ277" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR277" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS277" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="AT277" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU277" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV277" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -48723,12 +48713,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -48762,81 +48752,100 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="O278" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="R278" t="n">
-        <v>0.01162781954275227</v>
+        <v>0.3023975590469034</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR278" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
       <c r="AT278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48863,17 +48872,17 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -48907,22 +48916,39 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O279" t="n">
-        <v>11</v>
-      </c>
-      <c r="R279" t="n">
-        <v>0.1945873408375057</v>
-      </c>
-      <c r="S279" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>17</v>
       </c>
       <c r="U279" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>Streptococcus pneumoniae</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -48930,6 +48956,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ279" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
+        </is>
+      </c>
+      <c r="AM279" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN279" t="b">
+        <v>1</v>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -48942,7 +49026,7 @@
       </c>
       <c r="AQ279" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR279" t="inlineStr">
@@ -48952,7 +49036,7 @@
       </c>
       <c r="AS279" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
       <c r="AT279" t="n">
@@ -48960,47 +49044,47 @@
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -49027,17 +49111,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -49071,175 +49155,81 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O280" t="n">
-        <v>11</v>
-      </c>
-      <c r="U280" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V280" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W280" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X280" t="inlineStr">
-        <is>
-          <t>Syst. pneumokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y280" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z280" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA280" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB280" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC280" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD280" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE280" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF280" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG280" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH280" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI280" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ280" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK280" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
-        </is>
-      </c>
-      <c r="AM280" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN280" t="b">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0.01162781954275227</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO280" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ280" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR280" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS280" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr"/>
       <c r="AT280" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -49271,12 +49261,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -49301,7 +49291,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -49310,81 +49300,100 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="O281" t="n">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="R281" t="n">
-        <v>0.02263380124887814</v>
+        <v>0.1945873408375057</v>
       </c>
       <c r="S281" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR281" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS281" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT281" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA281" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB281" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC281" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -49411,123 +49420,507 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>11</v>
+      </c>
+      <c r="O282" t="n">
+        <v>11</v>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>Syst. pneumokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD282" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ282" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK282" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
+        </is>
+      </c>
+      <c r="AM282" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN282" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr">
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>79</v>
+      </c>
+      <c r="O283" t="n">
+        <v>79</v>
+      </c>
+      <c r="R283" t="n">
+        <v>0.02263380124887814</v>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr"/>
+      <c r="AT283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV283" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA283" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB283" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC283" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr">
+      <c r="G284" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>D106</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>Invasive pneumococcal disease</t>
-        </is>
-      </c>
-      <c r="J282" t="inlineStr">
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
         <is>
           <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
+      <c r="K284" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
+      <c r="L284" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M282" t="inlineStr">
+      <c r="M284" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N282" t="n">
+      <c r="N284" t="n">
         <v>18</v>
       </c>
-      <c r="O282" t="n">
+      <c r="O284" t="n">
         <v>18</v>
       </c>
-      <c r="R282" t="n">
+      <c r="R284" t="n">
         <v>0.01470255133618379</v>
       </c>
-      <c r="S282" t="inlineStr">
+      <c r="S284" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO282" t="inlineStr">
+      <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP282" t="inlineStr">
+      <c r="AP284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR282" t="inlineStr">
+      <c r="AR284" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS282" t="inlineStr"/>
-      <c r="AT282" t="n">
+      <c r="AS284" t="inlineStr"/>
+      <c r="AT284" t="n">
         <v>0</v>
       </c>
-      <c r="AU282" t="inlineStr">
+      <c r="AU284" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV282" t="inlineStr">
+      <c r="AV284" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW282" t="inlineStr">
+      <c r="AW284" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX282" t="inlineStr">
+      <c r="AX284" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY282" t="inlineStr">
+      <c r="AY284" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ282" t="inlineStr">
+      <c r="AZ284" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA282" t="inlineStr">
+      <c r="BA284" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB282" t="inlineStr">
+      <c r="BB284" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC282" t="inlineStr">
+      <c r="BC284" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -49649,7 +50042,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10">
@@ -49659,7 +50052,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11">
@@ -49679,7 +50072,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -49711,7 +50104,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13077</v>
+        <v>13189</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -49300,13 +49300,13 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="O281" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="R281" t="n">
-        <v>0.1945873408375057</v>
+        <v>0.5130029894806968</v>
       </c>
       <c r="S281" t="inlineStr">
         <is>
@@ -49464,10 +49464,10 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="O282" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="U282" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13189</v>
+        <v>13207</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -48752,13 +48752,13 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O278" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="R278" t="n">
-        <v>0.3023975590469034</v>
+        <v>0.4091261092987516</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -48916,10 +48916,10 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O279" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="U279" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13207</v>
+        <v>13213</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -35706,13 +35706,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O201" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="R201" t="n">
-        <v>1.05042418038266</v>
+        <v>1.0577698040217</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -43698,13 +43698,13 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O249" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R249" t="n">
-        <v>0.04844924809480115</v>
+        <v>0.05038721801859319</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -49155,13 +49155,13 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O280" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R280" t="n">
-        <v>0.01162781954275227</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
@@ -49923,6 +49923,545 @@
       <c r="BC284" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N285" t="n">
+        <v>2</v>
+      </c>
+      <c r="O285" t="n">
+        <v>2</v>
+      </c>
+      <c r="P285" t="n">
+        <v>2</v>
+      </c>
+      <c r="R285" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO285" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP285" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ285" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV285" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA285" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB285" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC285" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N286" t="n">
+        <v>2</v>
+      </c>
+      <c r="O286" t="n">
+        <v>2</v>
+      </c>
+      <c r="P286" t="n">
+        <v>2</v>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD286" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ286" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK286" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM286" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN286" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP286" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ286" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT286" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU286" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV286" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA286" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB286" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC286" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>97</v>
+      </c>
+      <c r="O287" t="n">
+        <v>97</v>
+      </c>
+      <c r="R287" t="n">
+        <v>0.02779086988786304</v>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR287" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr"/>
+      <c r="AT287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV287" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA287" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB287" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC287" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -49959,7 +50498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -50042,7 +50581,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
@@ -50052,7 +50591,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11">
@@ -50072,7 +50611,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -50104,7 +50643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13213</v>
+        <v>13319</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -35706,13 +35706,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O201" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="R201" t="n">
-        <v>1.0577698040217</v>
+        <v>1.061442615841219</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -42298,13 +42298,13 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O240" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="R240" t="n">
-        <v>1.094497922216898</v>
+        <v>1.090825110397378</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -42298,13 +42298,13 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O240" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="R240" t="n">
-        <v>1.090825110397378</v>
+        <v>1.094497922216898</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -43659,12 +43659,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -43698,13 +43698,13 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="O249" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="R249" t="n">
-        <v>0.05038721801859319</v>
+        <v>0.09486891961376966</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -43737,42 +43737,42 @@
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -43804,12 +43804,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -43843,100 +43843,81 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="O250" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="R250" t="n">
-        <v>0.6014517807704721</v>
+        <v>0.05038721801859319</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA250" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ250" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR250" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr"/>
       <c r="AT250" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -43963,7 +43944,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -44012,98 +43993,23 @@
       <c r="O251" t="n">
         <v>34</v>
       </c>
+      <c r="R251" t="n">
+        <v>0.6014517807704721</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U251" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>Syst. pneumokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE251" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF251" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG251" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
-        </is>
-      </c>
-      <c r="AM251" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN251" t="b">
-        <v>1</v>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
@@ -44202,17 +44108,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -44246,22 +44152,39 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="O252" t="n">
-        <v>112</v>
-      </c>
-      <c r="R252" t="n">
-        <v>2.118211722448449</v>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>34</v>
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>Syst. pneumokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -44269,6 +44192,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN252" t="b">
+        <v>1</v>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -44276,7 +44257,7 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
@@ -44284,57 +44265,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS252" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
       <c r="AT252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -44361,7 +44347,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -44410,98 +44396,23 @@
       <c r="O253" t="n">
         <v>112</v>
       </c>
+      <c r="R253" t="n">
+        <v>2.118211722448449</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U253" t="inlineStr">
         <is>
           <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>Invasive pneumococcal disease</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE253" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF253" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG253" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly invasive pneumococcal disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN253" t="b">
-        <v>1</v>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
@@ -44595,17 +44506,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -44639,22 +44550,39 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="O254" t="n">
-        <v>45</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0.4205196192727506</v>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>112</v>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -44662,6 +44590,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly invasive pneumococcal disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN254" t="b">
+        <v>1</v>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -44669,7 +44655,7 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ254" t="inlineStr">
@@ -44677,62 +44663,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR254" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS254" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+          <t>SER_NZ_INVASIVE_PNEUMOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44759,7 +44740,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -44808,98 +44789,23 @@
       <c r="O255" t="n">
         <v>45</v>
       </c>
+      <c r="R255" t="n">
+        <v>0.4205196192727506</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U255" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
         </is>
       </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>Invasiv pneumokockinfektion</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN255" t="b">
-        <v>1</v>
       </c>
       <c r="AO255" t="inlineStr">
         <is>
@@ -44998,17 +44904,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45042,81 +44948,175 @@
         </is>
       </c>
       <c r="N256" t="n">
+        <v>45</v>
+      </c>
+      <c r="O256" t="n">
+        <v>45</v>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>Invasiv pneumokockinfektion</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM invasive category.</t>
+        </is>
+      </c>
+      <c r="AM256" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN256" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNEUMOCOCCAL_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AT256" t="n">
         <v>2</v>
       </c>
-      <c r="O256" t="n">
-        <v>2</v>
-      </c>
-      <c r="R256" t="n">
-        <v>0.008691384892873792</v>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO256" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP256" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
-      <c r="AT256" t="n">
-        <v>0</v>
-      </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -45148,12 +45148,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -45187,13 +45187,13 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="O257" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="R257" t="n">
-        <v>0.01919575548955488</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -45226,42 +45226,42 @@
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -45293,12 +45293,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45323,7 +45323,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -45332,13 +45332,13 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="O258" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="R258" t="n">
-        <v>0.02450425222697299</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -45371,42 +45371,42 @@
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45438,12 +45438,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45477,93 +45477,81 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="O259" t="n">
-        <v>1</v>
-      </c>
-      <c r="P259" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="R259" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.02450425222697299</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA259" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ259" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45590,7 +45578,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -45642,98 +45630,18 @@
       <c r="P260" t="n">
         <v>1</v>
       </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W260" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X260" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y260" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R260" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD260" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE260" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF260" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG260" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ260" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK260" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM260" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN260" t="b">
-        <v>1</v>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
@@ -45827,17 +45735,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -45862,7 +45770,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -45871,81 +45779,173 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="O261" t="n">
-        <v>58</v>
-      </c>
-      <c r="R261" t="n">
-        <v>0.01661722117006243</v>
-      </c>
-      <c r="S261" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P261" t="n">
+        <v>1</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM261" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN261" t="b">
+        <v>1</v>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -45977,12 +45977,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -46007,7 +46007,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -46016,13 +46016,13 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="O262" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="R262" t="n">
-        <v>0.01470255133618379</v>
+        <v>0.01661722117006243</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
@@ -46055,42 +46055,42 @@
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46122,12 +46122,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46161,93 +46161,81 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O263" t="n">
-        <v>2</v>
-      </c>
-      <c r="P263" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="R263" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.01470255133618379</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA263" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ263" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr"/>
       <c r="AT263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46274,7 +46262,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -46326,98 +46314,18 @@
       <c r="P264" t="n">
         <v>2</v>
       </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V264" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W264" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X264" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y264" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R264" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD264" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE264" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF264" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG264" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH264" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI264" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ264" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK264" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM264" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN264" t="b">
-        <v>1</v>
       </c>
       <c r="AO264" t="inlineStr">
         <is>
@@ -46511,17 +46419,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46546,7 +46454,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -46555,81 +46463,173 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="O265" t="n">
-        <v>76</v>
-      </c>
-      <c r="R265" t="n">
-        <v>0.02177428980904733</v>
-      </c>
-      <c r="S265" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P265" t="n">
+        <v>2</v>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ265" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK265" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM265" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN265" t="b">
+        <v>1</v>
       </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR265" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46661,12 +46661,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46691,7 +46691,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -46700,13 +46700,13 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="O266" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="R266" t="n">
-        <v>0.02368744381940722</v>
+        <v>0.02177428980904733</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -46739,42 +46739,42 @@
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -46806,12 +46806,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -46845,93 +46845,81 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="O267" t="n">
-        <v>2</v>
-      </c>
-      <c r="P267" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="R267" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.02368744381940722</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ267" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46958,7 +46946,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -47010,98 +46998,18 @@
       <c r="P268" t="n">
         <v>2</v>
       </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V268" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W268" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X268" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y268" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R268" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD268" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE268" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF268" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG268" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI268" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ268" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK268" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM268" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN268" t="b">
-        <v>1</v>
       </c>
       <c r="AO268" t="inlineStr">
         <is>
@@ -47195,17 +47103,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47230,7 +47138,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -47239,81 +47147,173 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="O269" t="n">
-        <v>52</v>
-      </c>
-      <c r="R269" t="n">
-        <v>0.0148981982904008</v>
-      </c>
-      <c r="S269" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P269" t="n">
+        <v>2</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN269" t="b">
+        <v>1</v>
       </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR269" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47345,12 +47345,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47375,7 +47375,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -47384,13 +47384,13 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="O270" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="R270" t="n">
-        <v>0.01551935974374956</v>
+        <v>0.0148981982904008</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -47423,42 +47423,42 @@
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47490,12 +47490,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47529,93 +47529,81 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="O271" t="n">
-        <v>2</v>
-      </c>
-      <c r="P271" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R271" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.01551935974374956</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ271" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr"/>
       <c r="AT271" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47642,7 +47630,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -47686,106 +47674,26 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P272" t="n">
-        <v>2</v>
-      </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y272" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+        <v>1</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG272" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ272" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK272" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM272" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN272" t="b">
-        <v>1</v>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
@@ -47879,17 +47787,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -47914,7 +47822,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -47923,81 +47831,173 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="O273" t="n">
-        <v>67</v>
-      </c>
-      <c r="R273" t="n">
-        <v>0.01919575548955488</v>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P273" t="n">
+        <v>1</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
+        <v>1</v>
       </c>
       <c r="AO273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR273" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT273" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48029,12 +48029,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -48059,7 +48059,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="O274" t="n">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="R274" t="n">
-        <v>0.02532106063453875</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -48107,42 +48107,42 @@
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -48174,12 +48174,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -48213,93 +48213,81 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="O275" t="n">
-        <v>2</v>
-      </c>
-      <c r="P275" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="R275" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.02532106063453875</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA275" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO275" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ275" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS275" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr"/>
       <c r="AT275" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48326,7 +48314,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -48378,98 +48366,18 @@
       <c r="P276" t="n">
         <v>2</v>
       </c>
-      <c r="U276" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V276" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W276" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X276" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y276" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R276" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD276" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE276" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF276" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG276" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH276" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI276" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ276" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK276" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM276" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN276" t="b">
-        <v>1</v>
       </c>
       <c r="AO276" t="inlineStr">
         <is>
@@ -48563,17 +48471,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -48598,90 +48506,182 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N277" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O277" t="n">
-        <v>4</v>
-      </c>
-      <c r="R277" t="n">
-        <v>0.01469124727807916</v>
-      </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P277" t="n">
+        <v>2</v>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN277" t="b">
+        <v>1</v>
       </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR277" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS277" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
       <c r="AT277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48713,12 +48713,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -48752,100 +48752,81 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="O278" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="R278" t="n">
-        <v>0.4091261092987516</v>
+        <v>0.01469124727807916</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="AA278" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ278" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR278" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr"/>
       <c r="AT278" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -48872,7 +48853,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -48916,103 +48897,28 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="O279" t="n">
-        <v>23</v>
+        <v>28</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0.4980665678419585</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U279" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1390</t>
         </is>
       </c>
-      <c r="V279" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1390</t>
-        </is>
-      </c>
-      <c r="W279" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X279" t="inlineStr">
-        <is>
-          <t>Streptococcus pneumoniae</t>
-        </is>
-      </c>
-      <c r="Y279" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z279" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA279" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB279" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC279" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD279" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE279" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF279" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG279" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH279" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI279" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ279" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK279" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
-        </is>
-      </c>
-      <c r="AM279" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN279" t="b">
-        <v>1</v>
       </c>
       <c r="AO279" t="inlineStr">
         <is>
@@ -49111,17 +49017,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -49155,81 +49061,175 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="O280" t="n">
-        <v>10</v>
-      </c>
-      <c r="R280" t="n">
-        <v>0.01937969923792046</v>
-      </c>
-      <c r="S280" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>Streptococcus pneumoniae</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD280" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI280" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ280" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK280" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
+        </is>
+      </c>
+      <c r="AM280" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN280" t="b">
+        <v>1</v>
       </c>
       <c r="AO280" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR280" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS280" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
       <c r="AT280" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -49261,12 +49261,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -49300,100 +49300,81 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="O281" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="R281" t="n">
-        <v>0.5130029894806968</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="S281" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA281" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO281" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ281" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR281" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS281" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr"/>
       <c r="AT281" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA281" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB281" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC281" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -49420,7 +49401,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -49464,103 +49445,28 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="O282" t="n">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0.6722108138022923</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U282" t="inlineStr">
         <is>
           <t>SER_NO_FHI_708_MONTHLY</t>
         </is>
       </c>
-      <c r="V282" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_708_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W282" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X282" t="inlineStr">
-        <is>
-          <t>Syst. pneumokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y282" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z282" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA282" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB282" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC282" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD282" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE282" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF282" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG282" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH282" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI282" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ282" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK282" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
-        </is>
-      </c>
-      <c r="AM282" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN282" t="b">
-        <v>1</v>
       </c>
       <c r="AO282" t="inlineStr">
         <is>
@@ -49659,17 +49565,17 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -49694,7 +49600,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -49703,81 +49609,175 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="O283" t="n">
-        <v>79</v>
-      </c>
-      <c r="R283" t="n">
-        <v>0.02263380124887814</v>
-      </c>
-      <c r="S283" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>38</v>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>Syst. pneumokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ283" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK283" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic pneumococcal category.</t>
+        </is>
+      </c>
+      <c r="AM283" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN283" t="b">
+        <v>1</v>
       </c>
       <c r="AO283" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR283" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS283" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_708_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT283" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV283" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA283" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB283" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC283" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -49809,12 +49809,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -49839,7 +49839,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -49848,13 +49848,13 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="O284" t="n">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="R284" t="n">
-        <v>0.01470255133618379</v>
+        <v>0.02263380124887814</v>
       </c>
       <c r="S284" t="inlineStr">
         <is>
@@ -49887,42 +49887,42 @@
       </c>
       <c r="AV284" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA284" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB284" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC284" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -49954,12 +49954,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -49993,93 +49993,81 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O285" t="n">
-        <v>2</v>
-      </c>
-      <c r="P285" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="R285" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.01470255133618379</v>
       </c>
       <c r="S285" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA285" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO285" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ285" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS285" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR285" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr"/>
       <c r="AT285" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV285" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA285" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB285" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC285" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -50106,7 +50094,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -50158,98 +50146,18 @@
       <c r="P286" t="n">
         <v>2</v>
       </c>
-      <c r="U286" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="V286" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
-        </is>
-      </c>
-      <c r="W286" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X286" t="inlineStr">
-        <is>
-          <t>Pneumococcal Disease (invasive)</t>
-        </is>
-      </c>
-      <c r="Y286" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z286" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R286" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB286" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC286" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD286" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE286" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF286" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG286" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH286" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI286" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ286" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK286" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM286" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN286" t="b">
-        <v>1</v>
       </c>
       <c r="AO286" t="inlineStr">
         <is>
@@ -50343,123 +50251,1044 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>2</v>
+      </c>
+      <c r="O287" t="n">
+        <v>2</v>
+      </c>
+      <c r="P287" t="n">
+        <v>2</v>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF287" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG287" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH287" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI287" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ287" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK287" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM287" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN287" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT287" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV287" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA287" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB287" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC287" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr">
+      <c r="F288" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr">
+      <c r="G288" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>D106</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>Invasive pneumococcal disease</t>
-        </is>
-      </c>
-      <c r="J287" t="inlineStr">
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
         <is>
           <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr">
+      <c r="K288" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr">
+      <c r="L288" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="M287" t="inlineStr">
+      <c r="M288" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N287" t="n">
+      <c r="N288" t="n">
         <v>97</v>
       </c>
-      <c r="O287" t="n">
+      <c r="O288" t="n">
         <v>97</v>
       </c>
-      <c r="R287" t="n">
+      <c r="R288" t="n">
         <v>0.02779086988786304</v>
       </c>
-      <c r="S287" t="inlineStr">
+      <c r="S288" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO287" t="inlineStr">
+      <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP287" t="inlineStr">
+      <c r="AP288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR287" t="inlineStr">
+      <c r="AR288" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS287" t="inlineStr"/>
-      <c r="AT287" t="n">
+      <c r="AS288" t="inlineStr"/>
+      <c r="AT288" t="n">
         <v>0</v>
       </c>
-      <c r="AU287" t="inlineStr">
+      <c r="AU288" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV287" t="inlineStr">
+      <c r="AV288" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW287" t="inlineStr">
+      <c r="AW288" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX287" t="inlineStr">
+      <c r="AX288" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY287" t="inlineStr">
+      <c r="AY288" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ287" t="inlineStr">
+      <c r="AZ288" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA287" t="inlineStr">
+      <c r="BA288" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB287" t="inlineStr">
+      <c r="BB288" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC287" t="inlineStr">
+      <c r="BC288" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>17</v>
+      </c>
+      <c r="O289" t="n">
+        <v>17</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0.01388574292861803</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP289" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr"/>
+      <c r="AT289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV289" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA289" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB289" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC289" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>2</v>
+      </c>
+      <c r="O290" t="n">
+        <v>2</v>
+      </c>
+      <c r="P290" t="n">
+        <v>2</v>
+      </c>
+      <c r="R290" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP290" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ290" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS290" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT290" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU290" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV290" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA290" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB290" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC290" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>2</v>
+      </c>
+      <c r="O291" t="n">
+        <v>2</v>
+      </c>
+      <c r="P291" t="n">
+        <v>2</v>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC291" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD291" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF291" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG291" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH291" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI291" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ291" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK291" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM291" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN291" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO291" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP291" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ291" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU291" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV291" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW291" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX291" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY291" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA291" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB291" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC291" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>74</v>
+      </c>
+      <c r="O292" t="n">
+        <v>74</v>
+      </c>
+      <c r="R292" t="n">
+        <v>0.02120128218249345</v>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO292" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP292" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR292" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS292" t="inlineStr"/>
+      <c r="AT292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU292" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV292" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW292" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX292" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY292" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA292" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB292" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC292" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -50498,7 +51327,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -50581,7 +51410,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -50591,7 +51420,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11">
@@ -50611,7 +51440,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
@@ -50643,7 +51472,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13319</v>
+        <v>13436</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -42298,13 +42298,13 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O240" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="R240" t="n">
-        <v>1.094497922216898</v>
+        <v>1.098170734036417</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -48752,13 +48752,13 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>4</v>
+        <v>230</v>
       </c>
       <c r="O278" t="n">
-        <v>4</v>
+        <v>230</v>
       </c>
       <c r="R278" t="n">
-        <v>0.01469124727807916</v>
+        <v>0.8447467184895516</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -48897,13 +48897,13 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="O279" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="R279" t="n">
-        <v>0.4980665678419585</v>
+        <v>0.6581593932197309</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
@@ -49061,10 +49061,10 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="O280" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="U280" t="inlineStr">
         <is>
@@ -49300,13 +49300,13 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O281" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R281" t="n">
-        <v>0.0251936090092966</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S281" t="inlineStr">
         <is>
@@ -51291,6 +51291,1238 @@
       <c r="BC292" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>16</v>
+      </c>
+      <c r="O293" t="n">
+        <v>16</v>
+      </c>
+      <c r="R293" t="n">
+        <v>0.01306893452105226</v>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO293" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP293" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR293" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS293" t="inlineStr"/>
+      <c r="AT293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU293" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV293" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW293" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX293" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY293" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA293" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB293" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC293" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N294" t="n">
+        <v>1</v>
+      </c>
+      <c r="O294" t="n">
+        <v>1</v>
+      </c>
+      <c r="P294" t="n">
+        <v>1</v>
+      </c>
+      <c r="R294" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO294" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP294" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ294" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS294" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU294" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV294" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW294" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX294" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY294" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA294" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB294" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC294" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N295" t="n">
+        <v>1</v>
+      </c>
+      <c r="O295" t="n">
+        <v>1</v>
+      </c>
+      <c r="P295" t="n">
+        <v>1</v>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>Pneumococcal Disease (invasive)</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD295" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE295" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF295" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG295" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH295" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI295" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ295" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK295" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM295" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN295" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO295" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP295" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ295" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS295" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_INVASIVE_PNEUMOCOCCAL_DISEASE; SER_SG_HIST_INVASIVE_PNEUMOCOCCAL_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT295" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU295" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV295" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW295" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX295" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY295" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA295" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB295" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC295" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N296" t="n">
+        <v>94</v>
+      </c>
+      <c r="O296" t="n">
+        <v>94</v>
+      </c>
+      <c r="R296" t="n">
+        <v>0.02693135844803222</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO296" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP296" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR296" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS296" t="inlineStr"/>
+      <c r="AT296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU296" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV296" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW296" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX296" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY296" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA296" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB296" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC296" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N297" t="n">
+        <v>0</v>
+      </c>
+      <c r="O297" t="n">
+        <v>0</v>
+      </c>
+      <c r="R297" t="n">
+        <v>0</v>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO297" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP297" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ297" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR297" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS297" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="AT297" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU297" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV297" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW297" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX297" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY297" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA297" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB297" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC297" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N298" t="n">
+        <v>0</v>
+      </c>
+      <c r="O298" t="n">
+        <v>0</v>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>Streptococcus pneumoniae</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD298" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF298" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG298" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH298" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI298" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ298" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK298" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL register category; preserve source definition in series metadata.</t>
+        </is>
+      </c>
+      <c r="AM298" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN298" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO298" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP298" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ298" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR298" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS298" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1390</t>
+        </is>
+      </c>
+      <c r="AT298" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU298" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV298" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW298" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX298" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY298" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA298" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB298" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC298" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N299" t="n">
+        <v>1</v>
+      </c>
+      <c r="O299" t="n">
+        <v>1</v>
+      </c>
+      <c r="R299" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO299" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP299" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR299" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS299" t="inlineStr"/>
+      <c r="AT299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU299" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV299" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW299" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX299" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY299" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA299" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB299" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC299" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -51327,7 +52559,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -51410,7 +52642,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10">
@@ -51420,7 +52652,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11">
@@ -51440,7 +52672,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -51472,7 +52704,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13436</v>
+        <v>13787</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -42298,13 +42298,13 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O240" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R240" t="n">
-        <v>1.098170734036417</v>
+        <v>1.105516357675457</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -48752,13 +48752,13 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O278" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="R278" t="n">
-        <v>0.8447467184895516</v>
+        <v>0.8520923421285913</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13787</v>
+        <v>13791</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -19389,7 +19389,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -24866,7 +24866,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -31882,7 +31882,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -38329,7 +38329,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -44244,7 +44244,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -48897,13 +48897,13 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O279" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R279" t="n">
-        <v>0.6581593932197309</v>
+        <v>0.6937355766370136</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
@@ -49061,10 +49061,10 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O280" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U280" t="inlineStr">
         <is>
@@ -49445,13 +49445,13 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O282" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R282" t="n">
-        <v>0.6722108138022923</v>
+        <v>0.8137288798659329</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>
@@ -49609,10 +49609,10 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O283" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="U283" t="inlineStr">
         <is>
@@ -49701,7 +49701,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -52704,7 +52704,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13791</v>
+        <v>13801</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -60209,13 +60209,13 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R353" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S353" t="inlineStr">
         <is>
@@ -60465,7 +60465,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14854</v>
+        <v>14855</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -56407,13 +56407,13 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O326" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="R326" t="n">
-        <v>0.8814748366847496</v>
+        <v>0.8851476485042695</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
@@ -58151,13 +58151,13 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O337" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R337" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.03488345862825683</v>
       </c>
       <c r="S337" t="inlineStr">
         <is>
@@ -61863,13 +61863,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O358" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R358" t="n">
-        <v>0.1600928253777724</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S358" t="inlineStr">
         <is>
@@ -62027,10 +62027,10 @@
         </is>
       </c>
       <c r="N359" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O359" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U359" t="inlineStr">
         <is>
@@ -62266,13 +62266,13 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O360" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R360" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
@@ -63080,7 +63080,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15159</v>
+        <v>15165</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -56407,13 +56407,13 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="O326" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="R326" t="n">
-        <v>0.8851476485042695</v>
+        <v>0.8998388957823485</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
@@ -58151,13 +58151,13 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O337" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R337" t="n">
-        <v>0.03488345862825683</v>
+        <v>0.03682142855204888</v>
       </c>
       <c r="S337" t="inlineStr">
         <is>
@@ -61863,13 +61863,13 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O358" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R358" t="n">
-        <v>0.1778809170864138</v>
+        <v>0.284609467338262</v>
       </c>
       <c r="S358" t="inlineStr">
         <is>
@@ -62027,10 +62027,10 @@
         </is>
       </c>
       <c r="N359" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O359" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="U359" t="inlineStr">
         <is>
@@ -62266,13 +62266,13 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O360" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R360" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.02131766916171251</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
@@ -62416,13 +62416,13 @@
         </is>
       </c>
       <c r="N361" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="O361" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="R361" t="n">
-        <v>0.2122770990954608</v>
+        <v>0.5306927477386518</v>
       </c>
       <c r="S361" t="inlineStr">
         <is>
@@ -62580,10 +62580,10 @@
         </is>
       </c>
       <c r="N362" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="O362" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="U362" t="inlineStr">
         <is>
@@ -62899,6 +62899,151 @@
       <c r="BC363" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N364" t="n">
+        <v>22</v>
+      </c>
+      <c r="O364" t="n">
+        <v>22</v>
+      </c>
+      <c r="R364" t="n">
+        <v>0.01796978496644686</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO364" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP364" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR364" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS364" t="inlineStr"/>
+      <c r="AT364" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU364" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV364" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW364" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX364" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY364" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA364" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB364" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC364" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -62935,7 +63080,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -63018,7 +63163,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10">
@@ -63028,7 +63173,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11">
@@ -63080,7 +63225,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15165</v>
+        <v>15223</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d106/2026-2029.xlsx
+++ b/diseases/d106/2026-2029.xlsx
@@ -4702,9 +4702,6 @@
       <c r="O25" t="n">
         <v>10</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.002865038132769385</v>
       </c>
@@ -5397,9 +5394,6 @@
       <c r="O29" t="n">
         <v>265</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.07592351051838871</v>
       </c>
@@ -6092,9 +6086,6 @@
       <c r="O33" t="n">
         <v>201</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.05758726646866464</v>
       </c>
@@ -6787,9 +6778,6 @@
       <c r="O37" t="n">
         <v>186</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.05328970926951056</v>
       </c>
@@ -7482,9 +7470,6 @@
       <c r="O41" t="n">
         <v>177</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.05071117495001812</v>
       </c>
@@ -12096,9 +12081,6 @@
       <c r="O68" t="n">
         <v>197</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.0564412512155569</v>
       </c>
@@ -12791,9 +12773,6 @@
       <c r="O72" t="n">
         <v>178</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.05099767876329506</v>
       </c>
@@ -13486,9 +13465,6 @@
       <c r="O76" t="n">
         <v>219</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.06274433510764954</v>
       </c>
@@ -14181,9 +14157,6 @@
       <c r="O80" t="n">
         <v>224</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.06417685417403424</v>
       </c>
@@ -18813,9 +18786,6 @@
       <c r="O107" t="n">
         <v>173</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.04956515969691037</v>
       </c>
@@ -19508,9 +19478,6 @@
       <c r="O111" t="n">
         <v>195</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.05586824358900301</v>
       </c>
@@ -20203,9 +20170,6 @@
       <c r="O115" t="n">
         <v>187</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.0535762130827875</v>
       </c>
@@ -20898,9 +20862,6 @@
       <c r="O119" t="n">
         <v>184</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.05271670164295669</v>
       </c>
@@ -24797,13 +24758,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O142" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R142" t="n">
-        <v>1.355007662101085</v>
+        <v>1.345662781672802</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24961,10 +24922,10 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O143" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -25498,16 +25459,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O146" t="n">
-        <v>191</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="R146" t="n">
-        <v>0.05472222833589526</v>
+        <v>0.05443572452261833</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -26193,16 +26151,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O150" t="n">
-        <v>172</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="R150" t="n">
-        <v>0.04927865588363343</v>
+        <v>0.0489921520703565</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -26893,9 +26848,6 @@
       <c r="O154" t="n">
         <v>188</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.05386271689606444</v>
       </c>
@@ -27583,16 +27535,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O158" t="n">
-        <v>163</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="R158" t="n">
-        <v>0.04670012156414098</v>
+        <v>0.04641361775086404</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -32215,16 +32164,13 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O185" t="n">
-        <v>138</v>
-      </c>
-      <c r="Q185" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="R185" t="n">
-        <v>0.03953752623221752</v>
+        <v>0.03925102241894058</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
@@ -32915,9 +32861,6 @@
       <c r="O189" t="n">
         <v>135</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.0386780147923867</v>
       </c>
@@ -33610,9 +33553,6 @@
       <c r="O193" t="n">
         <v>173</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.04956515969691037</v>
       </c>
@@ -34305,9 +34245,6 @@
       <c r="O197" t="n">
         <v>28</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.00802210677175428</v>
       </c>
@@ -63044,6 +62981,156 @@
       <c r="BC364" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>invasive-pneumococcal-disease</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N365" t="n">
+        <v>117</v>
+      </c>
+      <c r="O365" t="n">
+        <v>117</v>
+      </c>
+      <c r="R365" t="n">
+        <v>0.03352094615340181</v>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO365" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP365" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR365" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS365" t="inlineStr"/>
+      <c r="AT365" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU365" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV365" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW365" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX365" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY365" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA365" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB365" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC365" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -63080,7 +63167,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -63163,7 +63250,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -63173,7 +63260,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11">
@@ -63225,7 +63312,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15223</v>
+        <v>15335</v>
       </c>
     </row>
     <row r="16">
